--- a/backend/data/uploads/MES/2026-07-05_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-05_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E9D2AA2-3C3C-4CC7-BABA-81505F6FACBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90BFDA7C-C30C-453A-9176-A0F9636C208C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{91F9A1DD-761E-4E42-AAF4-CB274CAB7B39}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C62478ED-C8E1-400B-AB55-F0C2C851283E}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F7A759-BF59-4E4D-8B7B-89548CE9DCE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6F1213-1858-4CB4-91A0-07343284AD4E}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-05_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-05_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90BFDA7C-C30C-453A-9176-A0F9636C208C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28EF9BDD-B5F4-4311-B415-8DE96B094378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C62478ED-C8E1-400B-AB55-F0C2C851283E}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{735B5E66-D9AD-4F8E-A3D0-2397A98E0FE5}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6F1213-1858-4CB4-91A0-07343284AD4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837B6A4A-1EC0-4B15-B23F-B7EB30177E8F}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-05_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-05_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28EF9BDD-B5F4-4311-B415-8DE96B094378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EC565A5-E74A-46F1-AE1E-84E103C8A1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{735B5E66-D9AD-4F8E-A3D0-2397A98E0FE5}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{785BCC50-EE35-4578-B8A9-2B59BCB32B48}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837B6A4A-1EC0-4B15-B23F-B7EB30177E8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA636AA6-FAB4-4DDA-B751-CD6B5B1072CC}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
